--- a/fomo_two_papers/deliverables/paper1/Paper1_Data.xlsx
+++ b/fomo_two_papers/deliverables/paper1/Paper1_Data.xlsx
@@ -39435,7 +39435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -39640,6 +39640,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>تذکر: میانگین گویه‌ها فقط برای توصیف است؛ تحلیل مقاله‌ها بر پایهٔ مدل متغیر پنهان (بدون نمرهٔ ترکیبی) انجام شده است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>قواعد: گویهٔ معکوس ندارد. حداقل ۸۰٪ گویه‌های هر سازه باید پاسخ داده شده باشد، وگرنه نمرهٔ سازه گم‌شده است. نمرهٔ بالاتر یعنی شدت بیشتر سازه (در کیفیت تصمیم: کیفیت بهتر).</t>
         </is>
